--- a/output_test/phase1_e2e/dhs_uniforms_stage5.xlsx
+++ b/output_test/phase1_e2e/dhs_uniforms_stage5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,15 +488,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TADA TRADING &amp; CO LLC</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>Tennier LLC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.tennierindustries.com/?srsltid=AfmBOopegmLi_fCOrCHge7fjOhRAAyoLVYqkP_-UJ4sI8LQYxc2QN1mg</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>support@tennierindustries.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+14236630363</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SMYRNA, GA</t>
+          <t>SUNBRIGHT, TN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -506,36 +518,44 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TADA TRADING &amp; CO LLC - located in SMYRNA, GA - for Vehicle project requirements.</t>
+          <t>Tennier LLC operates two Tennessee manufacturing facilities and advertises 40 years of producing military and tactical uniforms (parkas, trousers, sleep systems), indicating strong in‑house uniform supply and manufacturing capability, but the provided information does not document government-specific security procedures, handling of FOUO/LES items, dedicated staff for securing automated systems, or prior government contract performance.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>['https://www.tennierindustries.com']</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>['sam_registered']</t>
+          <t>['sam_registered', 'hybrid_website_discovery', 'contact_scraping']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAPER WRITER, LLC</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>TOMAHAWK PERFORMANCE INC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://tomahawkperformance.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>contact@tomahawkperformance.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DECATUR, GA</t>
+          <t>NASHVILLE, TN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -545,431 +565,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PAPER WRITER, LLC - located in DECATUR, GA - for Vehicle project requirements.</t>
+          <t>Tomahawk Performance sells relevant products—advertising combat uniforms and a newly released HW/Combat Uniform (04/18/2025), branded items, and layering systems—indicating technical capability to supply uniforms, but the provided information shows no government contract history (Past winner: False, total contract value: $0) and no documented security, packaging/compliance, or FOUO/LES handling procedures required by the solicitation.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>['https://tomahawkperformance.com']</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FAST TRACK GRADING CONTRACTING LLC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://fasttrackgrading.com/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AUSTELL, GA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>FAST TRACK GRADING CONTRACTING LLC - located in AUSTELL, GA - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>['https://fasttrackgrading.com/']</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SUN HAN LLC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>www.sunhanllc.com</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Miami, FL</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SUN HAN LLC - located in Miami, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>['www.sunhanllc.com']</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Proud Ward Solutions LLC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Naples, FL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Proud Ward Solutions LLC - located in Naples, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OPULETTA LLC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.opuletta.com/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>DORAL, FL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>OPULETTA LLC - located in DORAL, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>['https://www.opuletta.com/']</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nadia Tavitian</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Miami, FL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Nadia Tavitian - located in Miami, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NICKSON GENERAL CONTRACTORS, INC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.nicksongeneral.com</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Memphis, TN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>50</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NICKSON GENERAL CONTRACTORS, INC - located in Memphis, TN - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>['https://www.nicksongeneral.com']</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FASHION CENTER DG LLC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>www.josegalindofashion.com</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Miami, FL</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FASHION CENTER DG LLC - located in Miami, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>['www.josegalindofashion.com']</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Blue Border Solutions LLC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kissimmee, FL</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>50</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Blue Border Solutions LLC - located in Kissimmee, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ALMYRATION LLC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Davie, FL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>50</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ALMYRATION LLC - located in Davie, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>75 Holdings LLC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Geneva, FL</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>sam_entity</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75 Holdings LLC - located in Geneva, FL - for Vehicle project requirements.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>['sam_registered']</t>
+          <t>['sam_registered', 'contact_scraping']</t>
         </is>
       </c>
     </row>
